--- a/artfynd/A 45352-2025 artfynd.xlsx
+++ b/artfynd/A 45352-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113713459</v>
+        <v>113713445</v>
       </c>
       <c r="B2" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698351</v>
+        <v>698454</v>
       </c>
       <c r="R2" t="n">
-        <v>7207072</v>
+        <v>7207084</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113713460</v>
+        <v>113713456</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698391</v>
+        <v>698300</v>
       </c>
       <c r="R3" t="n">
-        <v>7207147</v>
+        <v>7207007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113713444</v>
+        <v>113713457</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698414</v>
+        <v>698325</v>
       </c>
       <c r="R4" t="n">
-        <v>7207079</v>
+        <v>7207005</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113713461</v>
+        <v>113713458</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698413</v>
+        <v>698351</v>
       </c>
       <c r="R5" t="n">
-        <v>7207223</v>
+        <v>7207031</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113713458</v>
+        <v>113713460</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>698351</v>
+        <v>698391</v>
       </c>
       <c r="R6" t="n">
-        <v>7207031</v>
+        <v>7207147</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,37 +1185,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113713456</v>
+        <v>113713461</v>
       </c>
       <c r="B7" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>698300</v>
+        <v>698413</v>
       </c>
       <c r="R7" t="n">
-        <v>7207007</v>
+        <v>7207223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113713457</v>
+        <v>113713443</v>
       </c>
       <c r="B8" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1298,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>698325</v>
+        <v>698484</v>
       </c>
       <c r="R8" t="n">
-        <v>7207005</v>
+        <v>7207023</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,37 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113713462</v>
+        <v>113713459</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>698416</v>
+        <v>698351</v>
       </c>
       <c r="R9" t="n">
-        <v>7207230</v>
+        <v>7207072</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113713445</v>
+        <v>113713444</v>
       </c>
       <c r="B10" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>698454</v>
+        <v>698414</v>
       </c>
       <c r="R10" t="n">
-        <v>7207084</v>
+        <v>7207079</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1635,6 +1590,108 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113713462</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Anderstjärn, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698416</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7207230</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Sweco Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
